--- a/data/trans_orig/P2C_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76604</t>
+          <t>75327</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112099</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82496</t>
+          <t>82195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116174</t>
+          <t>116341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>167467</t>
+          <t>172292</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218690</t>
+          <t>218323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381965</t>
+          <t>382224</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417460</t>
+          <t>418737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>351315</t>
+          <t>351148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>384993</t>
+          <t>385294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742863</t>
+          <t>743230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>794086</t>
+          <t>789261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>193929</t>
+          <t>195301</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>244548</t>
+          <t>243289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>294287</t>
+          <t>297590</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>346783</t>
+          <t>347752</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>502416</t>
+          <t>501775</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>575535</t>
+          <t>576442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490941</t>
+          <t>492200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>541560</t>
+          <t>540188</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278711</t>
+          <t>277742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331207</t>
+          <t>327904</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>785447</t>
+          <t>784540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>858566</t>
+          <t>859207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>329247</t>
+          <t>329316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>379604</t>
+          <t>378112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>381548</t>
+          <t>379653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>435437</t>
+          <t>434711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>722730</t>
+          <t>720191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>801842</t>
+          <t>794270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>259064</t>
+          <t>260556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309421</t>
+          <t>309352</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254307</t>
+          <t>255033</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>308196</t>
+          <t>310091</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>526570</t>
+          <t>534142</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>605682</t>
+          <t>608221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>147052</t>
+          <t>147573</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189707</t>
+          <t>191077</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111338</t>
+          <t>111746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152647</t>
+          <t>151052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>269140</t>
+          <t>268391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330493</t>
+          <t>327157</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,62%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329440</t>
+          <t>328070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372095</t>
+          <t>371574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362995</t>
+          <t>364590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>404304</t>
+          <t>403896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>704296</t>
+          <t>707632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>765649</t>
+          <t>766398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,06%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33026</t>
+          <t>32691</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>58563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59586</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91686</t>
+          <t>90837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101502</t>
+          <t>100949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141841</t>
+          <t>141829</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326458</t>
+          <t>328147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>353684</t>
+          <t>354019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>312300</t>
+          <t>313149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>344400</t>
+          <t>343794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>648855</t>
+          <t>648867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>689194</t>
+          <t>689747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43251</t>
+          <t>42971</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47602</t>
+          <t>47742</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73804</t>
+          <t>73481</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74537</t>
+          <t>74144</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107629</t>
+          <t>109510</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249332</t>
+          <t>249612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270360</t>
+          <t>271430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269130</t>
+          <t>269453</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>295332</t>
+          <t>295192</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527888</t>
+          <t>526007</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>560980</t>
+          <t>561373</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35779</t>
+          <t>35237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58734</t>
+          <t>57578</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61002</t>
+          <t>61071</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93560</t>
+          <t>92110</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104281</t>
+          <t>101796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142929</t>
+          <t>140613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>151149</t>
+          <t>152305</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174104</t>
+          <t>174646</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240348</t>
+          <t>241798</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>272906</t>
+          <t>272837</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>400862</t>
+          <t>403178</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>439510</t>
+          <t>441995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>899229</t>
+          <t>902370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1010203</t>
+          <t>1007998</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1110807</t>
+          <t>1112673</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1218215</t>
+          <t>1224850</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2042280</t>
+          <t>2052399</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2190236</t>
+          <t>2205057</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2266340</t>
+          <t>2268545</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2377314</t>
+          <t>2374173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2160982</t>
+          <t>2154347</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2268390</t>
+          <t>2266524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4465505</t>
+          <t>4450684</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4613461</t>
+          <t>4603342</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136984</t>
+          <t>138836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178580</t>
+          <t>177567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>175486</t>
+          <t>176244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216974</t>
+          <t>218237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>324384</t>
+          <t>323957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>385076</t>
+          <t>384039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275566</t>
+          <t>276579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>317162</t>
+          <t>315310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213256</t>
+          <t>211993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254744</t>
+          <t>253986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499300</t>
+          <t>500337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559992</t>
+          <t>560419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>243738</t>
+          <t>242703</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>296298</t>
+          <t>295741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>378169</t>
+          <t>379924</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>427622</t>
+          <t>430262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>639565</t>
+          <t>634901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713908</t>
+          <t>711735</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,86%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390789</t>
+          <t>391346</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443349</t>
+          <t>444384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182633</t>
+          <t>179993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>232086</t>
+          <t>230331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>583434</t>
+          <t>585607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657777</t>
+          <t>662441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>480962</t>
+          <t>478194</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>528066</t>
+          <t>528233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>556790</t>
+          <t>558752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>600242</t>
+          <t>600212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1052445</t>
+          <t>1049964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1117603</t>
+          <t>1117194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153797</t>
+          <t>153630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200901</t>
+          <t>203669</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110608</t>
+          <t>110638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154060</t>
+          <t>152098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275109</t>
+          <t>275518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>340267</t>
+          <t>342748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>296807</t>
+          <t>299199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>348496</t>
+          <t>352160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>249310</t>
+          <t>250994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>302975</t>
+          <t>304327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>561705</t>
+          <t>562026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>636093</t>
+          <t>637800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>266121</t>
+          <t>262457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317810</t>
+          <t>315418</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>313224</t>
+          <t>311872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366889</t>
+          <t>365205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>594723</t>
+          <t>593016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>669111</t>
+          <t>668790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97884</t>
+          <t>96082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135774</t>
+          <t>133268</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87615</t>
+          <t>86920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124815</t>
+          <t>125817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192866</t>
+          <t>192956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247794</t>
+          <t>248771</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>293655</t>
+          <t>296161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331545</t>
+          <t>333347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>322985</t>
+          <t>321983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360185</t>
+          <t>360880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>629435</t>
+          <t>628458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>684363</t>
+          <t>684273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57116</t>
+          <t>57269</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89515</t>
+          <t>89821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75201</t>
+          <t>75576</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109180</t>
+          <t>110030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>143181</t>
+          <t>145053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189235</t>
+          <t>189379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220271</t>
+          <t>219965</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252670</t>
+          <t>252517</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244816</t>
+          <t>243966</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278795</t>
+          <t>278420</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474547</t>
+          <t>474403</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520601</t>
+          <t>518729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,15%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75401</t>
+          <t>74812</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107285</t>
+          <t>108801</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162253</t>
+          <t>162267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203499</t>
+          <t>205188</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>248671</t>
+          <t>247016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>303228</t>
+          <t>298899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>142566</t>
+          <t>141050</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174450</t>
+          <t>175039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>185480</t>
+          <t>183791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>226726</t>
+          <t>226712</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>335602</t>
+          <t>339931</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>390159</t>
+          <t>391814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1478659</t>
+          <t>1475400</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1593946</t>
+          <t>1592229</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1776561</t>
+          <t>1777181</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1901319</t>
+          <t>1901415</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3270192</t>
+          <t>3291292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3452205</t>
+          <t>3461983</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1832833</t>
+          <t>1834550</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1948120</t>
+          <t>1951379</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1656990</t>
+          <t>1656894</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1781748</t>
+          <t>1781128</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3532883</t>
+          <t>3523105</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3714896</t>
+          <t>3693796</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79095</t>
+          <t>79891</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115640</t>
+          <t>115501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110390</t>
+          <t>108759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>147077</t>
+          <t>146088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>199608</t>
+          <t>200421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248822</t>
+          <t>248461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303823</t>
+          <t>303962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340368</t>
+          <t>339572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248678</t>
+          <t>249667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285365</t>
+          <t>286996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>566396</t>
+          <t>566757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>615610</t>
+          <t>614797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202533</t>
+          <t>200762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>248293</t>
+          <t>249065</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>305024</t>
+          <t>303082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>345923</t>
+          <t>349045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>516464</t>
+          <t>519538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>583412</t>
+          <t>583789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342203</t>
+          <t>341431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387963</t>
+          <t>389734</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217621</t>
+          <t>214499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>258520</t>
+          <t>260462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>570628</t>
+          <t>570251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>637576</t>
+          <t>634502</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>344588</t>
+          <t>347414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>397978</t>
+          <t>397312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>411477</t>
+          <t>412633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>456837</t>
+          <t>458439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>772035</t>
+          <t>771137</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>842197</t>
+          <t>842149</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271119</t>
+          <t>271785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324509</t>
+          <t>321683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204549</t>
+          <t>202947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>249909</t>
+          <t>248753</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488286</t>
+          <t>488334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>558448</t>
+          <t>559346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>174350</t>
+          <t>176859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223628</t>
+          <t>223974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178298</t>
+          <t>176894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224411</t>
+          <t>226630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>371093</t>
+          <t>368233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>436240</t>
+          <t>435927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>422420</t>
+          <t>422074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>471698</t>
+          <t>469189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424666</t>
+          <t>422447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470779</t>
+          <t>472183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>858885</t>
+          <t>859198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>924032</t>
+          <t>926892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47780</t>
+          <t>48611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79315</t>
+          <t>79370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57535</t>
+          <t>57522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88806</t>
+          <t>91967</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>111753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157071</t>
+          <t>157100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>398603</t>
+          <t>398548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>430138</t>
+          <t>429307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>408043</t>
+          <t>404882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439314</t>
+          <t>439327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>817696</t>
+          <t>817667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>862684</t>
+          <t>863014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>28159</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51326</t>
+          <t>50708</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48909</t>
+          <t>49566</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81052</t>
+          <t>79536</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84468</t>
+          <t>85533</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>122490</t>
+          <t>122046</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283004</t>
+          <t>283622</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>306480</t>
+          <t>306171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>296710</t>
+          <t>298226</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>328853</t>
+          <t>328196</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>589602</t>
+          <t>590046</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>627624</t>
+          <t>626559</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,99%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>56749</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82676</t>
+          <t>82461</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>127043</t>
+          <t>126862</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>170474</t>
+          <t>169291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190812</t>
+          <t>190109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>242130</t>
+          <t>243085</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>174322</t>
+          <t>174537</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>199892</t>
+          <t>200249</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>229695</t>
+          <t>230878</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>273126</t>
+          <t>273307</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>415037</t>
+          <t>414082</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>466355</t>
+          <t>467058</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1007995</t>
+          <t>1008815</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1110714</t>
+          <t>1117687</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1312864</t>
+          <t>1316269</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1434726</t>
+          <t>1436404</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2353086</t>
+          <t>2353450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2516177</t>
+          <t>2514349</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2283636</t>
+          <t>2276663</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2386355</t>
+          <t>2385535</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2109816</t>
+          <t>2108138</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2231678</t>
+          <t>2228273</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4422715</t>
+          <t>4424543</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4585806</t>
+          <t>4585442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45108</t>
+          <t>43783</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44558</t>
+          <t>43770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37520</t>
+          <t>38011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76195</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354879</t>
+          <t>356204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>385375</t>
+          <t>385876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268642</t>
+          <t>269430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294543</t>
+          <t>294437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>636992</t>
+          <t>636149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>675667</t>
+          <t>675176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35169</t>
+          <t>35701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70795</t>
+          <t>70241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56835</t>
+          <t>56223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116335</t>
+          <t>115964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107795</t>
+          <t>107926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172518</t>
+          <t>172348</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352752</t>
+          <t>353306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>388378</t>
+          <t>387846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>395758</t>
+          <t>396129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455258</t>
+          <t>455870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>763122</t>
+          <t>763292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>827845</t>
+          <t>827714</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,47%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90542</t>
+          <t>89739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131671</t>
+          <t>128522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97672</t>
+          <t>94878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148149</t>
+          <t>149633</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200869</t>
+          <t>205659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266166</t>
+          <t>268322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>404667</t>
+          <t>407816</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>445796</t>
+          <t>446599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443853</t>
+          <t>442369</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>494330</t>
+          <t>497124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>862174</t>
+          <t>860018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>927471</t>
+          <t>922681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40318</t>
+          <t>38988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132132</t>
+          <t>131477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80750</t>
+          <t>81698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114888</t>
+          <t>116207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108971</t>
+          <t>115495</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231340</t>
+          <t>232125</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>755654</t>
+          <t>756309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>847468</t>
+          <t>848798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597993</t>
+          <t>596674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>632131</t>
+          <t>631183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1369327</t>
+          <t>1368542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1491696</t>
+          <t>1485172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38326</t>
+          <t>37023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63820</t>
+          <t>62705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47204</t>
+          <t>47198</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68362</t>
+          <t>68361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89342</t>
+          <t>91610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121823</t>
+          <t>123387</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>497414</t>
+          <t>498529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>522908</t>
+          <t>524211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>479543</t>
+          <t>479544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>500701</t>
+          <t>500707</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>987316</t>
+          <t>985752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1019797</t>
+          <t>1017529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23211</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40300</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66540</t>
+          <t>66122</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>459184</t>
+          <t>441477</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93939</t>
+          <t>94416</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>596677</t>
+          <t>605054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>327865</t>
+          <t>327549</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>344954</t>
+          <t>345373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149184</t>
+          <t>166891</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>541828</t>
+          <t>542246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>379856</t>
+          <t>371479</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>882594</t>
+          <t>882117</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50852</t>
+          <t>50132</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72249</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121947</t>
+          <t>122161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148074</t>
+          <t>150467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>178807</t>
+          <t>177202</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214862</t>
+          <t>212137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210510</t>
+          <t>210645</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>231907</t>
+          <t>232627</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>277757</t>
+          <t>275364</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>303884</t>
+          <t>303670</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>493728</t>
+          <t>496453</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>529783</t>
+          <t>531388</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,99%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>332435</t>
+          <t>323099</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>462865</t>
+          <t>461845</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>608615</t>
+          <t>605896</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1348448</t>
+          <t>1323806</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>995109</t>
+          <t>1002271</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1864797</t>
+          <t>1713776</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2996952</t>
+          <t>2997972</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3127382</t>
+          <t>3136718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2363832</t>
+          <t>2388474</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3103665</t>
+          <t>3106384</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5307300</t>
+          <t>5458321</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6176988</t>
+          <t>6169826</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75327</t>
+          <t>77735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111840</t>
+          <t>111714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82195</t>
+          <t>81793</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116341</t>
+          <t>116686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>172292</t>
+          <t>169742</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218323</t>
+          <t>218647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>382224</t>
+          <t>382350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418737</t>
+          <t>416329</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>351148</t>
+          <t>350803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>385294</t>
+          <t>385696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>743230</t>
+          <t>742906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>789261</t>
+          <t>791811</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195301</t>
+          <t>192933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243289</t>
+          <t>244355</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>297590</t>
+          <t>294560</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>347752</t>
+          <t>346471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>501775</t>
+          <t>501838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>576442</t>
+          <t>576195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492200</t>
+          <t>491134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>540188</t>
+          <t>542556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>277742</t>
+          <t>279023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327904</t>
+          <t>330934</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>784540</t>
+          <t>784787</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859207</t>
+          <t>859144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>329316</t>
+          <t>324855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>378112</t>
+          <t>378047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>379653</t>
+          <t>378614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>434711</t>
+          <t>431572</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>720191</t>
+          <t>720843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>794270</t>
+          <t>796665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>260556</t>
+          <t>260621</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309352</t>
+          <t>313813</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>255033</t>
+          <t>258172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310091</t>
+          <t>311130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>534142</t>
+          <t>531747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>608221</t>
+          <t>607569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>147573</t>
+          <t>146702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191077</t>
+          <t>191343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111746</t>
+          <t>110736</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151052</t>
+          <t>151882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268391</t>
+          <t>270963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>327157</t>
+          <t>326819</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>328070</t>
+          <t>327804</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371574</t>
+          <t>372445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>364590</t>
+          <t>363760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>403896</t>
+          <t>404906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707632</t>
+          <t>707970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766398</t>
+          <t>763826</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32691</t>
+          <t>32934</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58563</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60192</t>
+          <t>60435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90837</t>
+          <t>90405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100949</t>
+          <t>102123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141829</t>
+          <t>142672</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328147</t>
+          <t>326761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>354019</t>
+          <t>353776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>313149</t>
+          <t>313581</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>343794</t>
+          <t>343551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>648867</t>
+          <t>648024</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>689747</t>
+          <t>688573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42971</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47742</t>
+          <t>46722</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73481</t>
+          <t>72726</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74144</t>
+          <t>73076</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109510</t>
+          <t>108040</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249612</t>
+          <t>249777</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271430</t>
+          <t>271274</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269453</t>
+          <t>270208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>295192</t>
+          <t>296212</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526007</t>
+          <t>527477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>561373</t>
+          <t>562441</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57578</t>
+          <t>59088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61071</t>
+          <t>61063</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92110</t>
+          <t>94679</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101796</t>
+          <t>103832</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140613</t>
+          <t>143796</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152305</t>
+          <t>150795</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174646</t>
+          <t>174146</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>241798</t>
+          <t>239229</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>272837</t>
+          <t>272845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>403178</t>
+          <t>399995</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>441995</t>
+          <t>439959</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>902370</t>
+          <t>907289</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1007998</t>
+          <t>1008885</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1112673</t>
+          <t>1109829</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1224850</t>
+          <t>1221313</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2052399</t>
+          <t>2046214</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2205057</t>
+          <t>2200666</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2268545</t>
+          <t>2267658</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2374173</t>
+          <t>2369254</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2154347</t>
+          <t>2157884</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2266524</t>
+          <t>2269368</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4450684</t>
+          <t>4455075</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4603342</t>
+          <t>4609527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138836</t>
+          <t>138483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177567</t>
+          <t>178765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176244</t>
+          <t>176910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>218237</t>
+          <t>218555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>323957</t>
+          <t>324314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>384039</t>
+          <t>382744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276579</t>
+          <t>275381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>315310</t>
+          <t>315663</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>211993</t>
+          <t>211675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253986</t>
+          <t>253320</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500337</t>
+          <t>501632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>560419</t>
+          <t>560062</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>242703</t>
+          <t>243779</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>295741</t>
+          <t>295219</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>379924</t>
+          <t>380079</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>430262</t>
+          <t>428704</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>634901</t>
+          <t>635973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>711735</t>
+          <t>709285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391346</t>
+          <t>391868</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>444384</t>
+          <t>443308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179993</t>
+          <t>181551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230331</t>
+          <t>230176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>585607</t>
+          <t>588057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>662441</t>
+          <t>661369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>478194</t>
+          <t>481611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>528233</t>
+          <t>528056</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>558752</t>
+          <t>555749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>600212</t>
+          <t>600116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1049964</t>
+          <t>1050371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1117194</t>
+          <t>1115114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153630</t>
+          <t>153807</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203669</t>
+          <t>200252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110638</t>
+          <t>110734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152098</t>
+          <t>155101</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275518</t>
+          <t>277598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>342748</t>
+          <t>342341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>299199</t>
+          <t>297472</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>352160</t>
+          <t>349460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>250994</t>
+          <t>248361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>304327</t>
+          <t>302812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>562026</t>
+          <t>562584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>637800</t>
+          <t>638335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262457</t>
+          <t>265157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>317145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>311872</t>
+          <t>313387</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365205</t>
+          <t>367838</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>593016</t>
+          <t>592481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>668790</t>
+          <t>668232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96082</t>
+          <t>98064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133268</t>
+          <t>136247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86920</t>
+          <t>86437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125817</t>
+          <t>125884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192956</t>
+          <t>195265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>248771</t>
+          <t>249010</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296161</t>
+          <t>293182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333347</t>
+          <t>331365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>321983</t>
+          <t>321916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360880</t>
+          <t>361363</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>628458</t>
+          <t>628219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>684273</t>
+          <t>681964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57269</t>
+          <t>58134</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89821</t>
+          <t>89488</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75576</t>
+          <t>76223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110030</t>
+          <t>109289</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>145053</t>
+          <t>144379</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189379</t>
+          <t>189787</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219965</t>
+          <t>220298</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252517</t>
+          <t>251652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243966</t>
+          <t>244707</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278420</t>
+          <t>277773</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474403</t>
+          <t>473995</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518729</t>
+          <t>519403</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74812</t>
+          <t>74973</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>108801</t>
+          <t>108689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162267</t>
+          <t>163641</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>205188</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>247016</t>
+          <t>245954</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>298899</t>
+          <t>300303</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141050</t>
+          <t>141162</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175039</t>
+          <t>174878</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>183791</t>
+          <t>184789</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>226712</t>
+          <t>225338</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>339931</t>
+          <t>338527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>391814</t>
+          <t>392876</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,5%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1475400</t>
+          <t>1473734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1592229</t>
+          <t>1595276</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1777181</t>
+          <t>1775443</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1901415</t>
+          <t>1895160</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3291292</t>
+          <t>3288658</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3461983</t>
+          <t>3459538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1834550</t>
+          <t>1831503</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1951379</t>
+          <t>1953045</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1656894</t>
+          <t>1663149</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1781128</t>
+          <t>1782866</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3523105</t>
+          <t>3525550</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3693796</t>
+          <t>3696430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79891</t>
+          <t>77893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115501</t>
+          <t>115019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>108759</t>
+          <t>109970</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146088</t>
+          <t>146423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200421</t>
+          <t>199042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248461</t>
+          <t>246433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303962</t>
+          <t>304444</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>339572</t>
+          <t>341570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249667</t>
+          <t>249332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286996</t>
+          <t>285785</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>566757</t>
+          <t>568785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>614797</t>
+          <t>616176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200762</t>
+          <t>199641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>249065</t>
+          <t>250096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>303082</t>
+          <t>303859</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>349045</t>
+          <t>348782</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>519538</t>
+          <t>516595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>583789</t>
+          <t>582935</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341431</t>
+          <t>340400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389734</t>
+          <t>390855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>214499</t>
+          <t>214762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>260462</t>
+          <t>259685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>570251</t>
+          <t>571105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>634502</t>
+          <t>637445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,24%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>347414</t>
+          <t>343760</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>397312</t>
+          <t>395827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>412633</t>
+          <t>409711</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>458439</t>
+          <t>456956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>771137</t>
+          <t>769745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>842149</t>
+          <t>840933</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271785</t>
+          <t>273270</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321683</t>
+          <t>325337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202947</t>
+          <t>204430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248753</t>
+          <t>251675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488334</t>
+          <t>489550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559346</t>
+          <t>560738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176859</t>
+          <t>174767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223974</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176894</t>
+          <t>180850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>226630</t>
+          <t>226202</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>368233</t>
+          <t>367744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>435927</t>
+          <t>440344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>422074</t>
+          <t>420191</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>469189</t>
+          <t>471281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>422447</t>
+          <t>422875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472183</t>
+          <t>468227</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>859198</t>
+          <t>854781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>926892</t>
+          <t>927381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48611</t>
+          <t>47219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79370</t>
+          <t>78745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57522</t>
+          <t>57314</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91967</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>114013</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157100</t>
+          <t>157815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>398548</t>
+          <t>399173</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>429307</t>
+          <t>430699</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>404882</t>
+          <t>405318</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439327</t>
+          <t>439535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>817667</t>
+          <t>816952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>863014</t>
+          <t>860754</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>27045</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>50155</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49566</t>
+          <t>49965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79536</t>
+          <t>80976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85533</t>
+          <t>84240</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>122046</t>
+          <t>122041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283622</t>
+          <t>284175</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>306171</t>
+          <t>307285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>298226</t>
+          <t>296786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>328196</t>
+          <t>327797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>590046</t>
+          <t>590051</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>626559</t>
+          <t>627852</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56749</t>
+          <t>56589</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82461</t>
+          <t>81785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126862</t>
+          <t>124324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169291</t>
+          <t>167039</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190109</t>
+          <t>189896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>243085</t>
+          <t>242485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>174537</t>
+          <t>175213</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200249</t>
+          <t>200409</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230878</t>
+          <t>233130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>273307</t>
+          <t>275845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>414082</t>
+          <t>414682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>467058</t>
+          <t>467271</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1008815</t>
+          <t>1007320</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1117687</t>
+          <t>1112032</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1316269</t>
+          <t>1312919</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1436404</t>
+          <t>1430779</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2353450</t>
+          <t>2351851</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2514349</t>
+          <t>2520436</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2276663</t>
+          <t>2282318</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2385535</t>
+          <t>2387030</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2108138</t>
+          <t>2113763</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2228273</t>
+          <t>2231623</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4424543</t>
+          <t>4418456</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4585442</t>
+          <t>4587041</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14111</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43783</t>
+          <t>52184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>25398</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43770</t>
+          <t>58267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54651</t>
+          <t>72427</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38011</t>
+          <t>52778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77038</t>
+          <t>99815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>374364</t>
+          <t>375990</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356204</t>
+          <t>355609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>385876</t>
+          <t>388220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>284172</t>
+          <t>321888</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269430</t>
+          <t>304245</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294437</t>
+          <t>337114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>658536</t>
+          <t>697878</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>636149</t>
+          <t>670490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>675176</t>
+          <t>717527</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49953</t>
+          <t>64371</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35701</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70241</t>
+          <t>85685</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>93048</t>
+          <t>107801</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56223</t>
+          <t>90507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115964</t>
+          <t>127126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>143001</t>
+          <t>172172</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107926</t>
+          <t>146120</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172348</t>
+          <t>203108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>373594</t>
+          <t>412519</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353306</t>
+          <t>391205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387846</t>
+          <t>429885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>419045</t>
+          <t>393932</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>396129</t>
+          <t>374607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455870</t>
+          <t>411226</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>792639</t>
+          <t>806451</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>763292</t>
+          <t>775515</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>827714</t>
+          <t>832503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>108561</t>
+          <t>128750</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89739</t>
+          <t>108480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128522</t>
+          <t>152596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>129079</t>
+          <t>150164</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94878</t>
+          <t>131176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149633</t>
+          <t>168149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>237640</t>
+          <t>278913</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205659</t>
+          <t>252706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268322</t>
+          <t>311489</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>427777</t>
+          <t>492087</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407816</t>
+          <t>468241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>446599</t>
+          <t>512357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>462923</t>
+          <t>473029</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442369</t>
+          <t>455044</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>497124</t>
+          <t>492017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>890700</t>
+          <t>965116</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>860018</t>
+          <t>932540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>922681</t>
+          <t>991323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88710</t>
+          <t>103116</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38988</t>
+          <t>83716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131477</t>
+          <t>124439</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>98556</t>
+          <t>112364</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81698</t>
+          <t>96606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116207</t>
+          <t>127817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>187266</t>
+          <t>215480</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115495</t>
+          <t>191491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232125</t>
+          <t>240853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>799076</t>
+          <t>597501</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>756309</t>
+          <t>576178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>848798</t>
+          <t>616901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>614325</t>
+          <t>624522</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>596674</t>
+          <t>609069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>631183</t>
+          <t>640280</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1413401</t>
+          <t>1222024</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1368542</t>
+          <t>1196651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1485172</t>
+          <t>1246013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>48449</t>
+          <t>51966</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37023</t>
+          <t>41166</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62705</t>
+          <t>66640</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>56686</t>
+          <t>64623</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47198</t>
+          <t>53424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68361</t>
+          <t>77607</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>105135</t>
+          <t>116589</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91610</t>
+          <t>99258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123387</t>
+          <t>135083</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>512785</t>
+          <t>557380</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498529</t>
+          <t>542706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>524211</t>
+          <t>568180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>491219</t>
+          <t>544232</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>479544</t>
+          <t>531248</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>500707</t>
+          <t>555431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1004004</t>
+          <t>1101613</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985752</t>
+          <t>1083119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1017529</t>
+          <t>1118944</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>34652</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40616</t>
+          <t>45498</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>252021</t>
+          <t>52390</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66122</t>
+          <t>43033</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>441477</t>
+          <t>62874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>283394</t>
+          <t>87042</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94416</t>
+          <t>74334</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>605054</t>
+          <t>101818</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>336792</t>
+          <t>372428</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>327549</t>
+          <t>361582</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>345373</t>
+          <t>380574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>356347</t>
+          <t>386776</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>166891</t>
+          <t>376292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>542246</t>
+          <t>396133</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>693139</t>
+          <t>759204</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371479</t>
+          <t>744428</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>882117</t>
+          <t>771912</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>60264</t>
+          <t>64218</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50132</t>
+          <t>52824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72114</t>
+          <t>77076</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>134874</t>
+          <t>145788</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>122161</t>
+          <t>130806</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150467</t>
+          <t>160757</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>195138</t>
+          <t>210005</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177202</t>
+          <t>191982</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212137</t>
+          <t>229185</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>222495</t>
+          <t>245980</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210645</t>
+          <t>233122</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232627</t>
+          <t>257374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>290957</t>
+          <t>318821</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>275364</t>
+          <t>303852</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>303670</t>
+          <t>333803</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>564802</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>496453</t>
+          <t>545622</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>531388</t>
+          <t>582825</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>412934</t>
+          <t>478875</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>323099</t>
+          <t>438065</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>461845</t>
+          <t>523629</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>793292</t>
+          <t>673754</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>605896</t>
+          <t>633462</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1323806</t>
+          <t>716404</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1206225</t>
+          <t>1152629</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1002271</t>
+          <t>1096644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1713776</t>
+          <t>1221522</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3046883</t>
+          <t>3053887</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2997972</t>
+          <t>3009133</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3136718</t>
+          <t>3094697</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2918988</t>
+          <t>3063200</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2388474</t>
+          <t>3020550</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3106384</t>
+          <t>3103492</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5965872</t>
+          <t>6117087</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5458321</t>
+          <t>6048194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6169826</t>
+          <t>6173072</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
